--- a/AI_Learning.xlsx
+++ b/AI_Learning.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
   <si>
     <t>Date</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>20260328_063053</t>
+  </si>
+  <si>
+    <t>20260513_044158</t>
   </si>
   <si>
     <t>Negative Sentiment Trend</t>
@@ -379,7 +382,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -418,16 +421,36 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
         <v>9</v>
+      </c>
+      <c r="E3">
+        <v>0.5</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
